--- a/data/raw/inventory/Week 29/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,86 +413,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>afn_fulfillable_quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>afn_inbound_working_quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>afn_inbound_shipped_quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>afn_inbound_receiving_quantity</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>afn_reserved_quantity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>afn_total_quantity</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>afn_unsellable_quantity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>afn_researching_quantity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Seller Account</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
@@ -1877,12 +1865,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA76723</t>
+          <t>FBA76725</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1892,14 +1880,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AM-C20</t>
+          <t>AM-C22</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1914,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1939,12 +1927,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA76725</t>
+          <t>FBA76726</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B0BLKD4815</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1954,14 +1942,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AM-C22</t>
+          <t>AM-C23</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1973,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2001,12 +1989,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA76726</t>
+          <t>FBA76730</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0BLKD4815</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2004,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AM-C23</t>
+          <t>AM-C27</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2063,12 +2051,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA76730</t>
+          <t>FBA76734</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0BLKB6FRR</t>
+          <t>B0BLKHVCDX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2078,14 +2066,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AM-C27</t>
+          <t>AA-07</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2100,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2125,12 +2113,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA76734</t>
+          <t>FBA76736</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0BLKHVCDX</t>
+          <t>B0BLS63XCL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2140,7 +2128,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AA-07</t>
+          <t>AA-09</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2187,12 +2175,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA76736</t>
+          <t>FBA76737</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0BLS63XCL</t>
+          <t>B0C59G1C4N</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2202,14 +2190,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AA-09</t>
+          <t>AA-10</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2224,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2249,12 +2237,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBA76737</t>
+          <t>FBA76739</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0C59G1C4N</t>
+          <t>B0BLRK37TB</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2264,14 +2252,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AA-10</t>
+          <t>AA-12</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2286,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2311,12 +2299,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA76739</t>
+          <t>FBA76742</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0BLRK37TB</t>
+          <t>B0BLKBJ5HN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2326,14 +2314,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AA-12</t>
+          <t>AM-K1</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2345,10 +2333,10 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2373,12 +2361,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FBA76742</t>
+          <t>FBA76743</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B0BLKBJ5HN</t>
+          <t>B0BLK8PXNY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2388,14 +2376,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AM-K1</t>
+          <t>AM-K2</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2407,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2435,12 +2423,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FBA76743</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0BLK8PXNY</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2450,7 +2438,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AM-K2</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2497,12 +2485,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA76863</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2512,14 +2500,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2531,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2559,12 +2547,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBA76863</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2574,14 +2562,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2593,10 +2581,10 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2621,12 +2609,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA77011</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BPMN89NG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2636,14 +2624,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-C29</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2655,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2683,12 +2671,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FBA77011</t>
+          <t>FBA77171</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B0BPMN89NG</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2698,14 +2686,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AM-C29</t>
+          <t>AC-6XL</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2720,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2745,12 +2733,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FBA77171</t>
+          <t>FBA78203</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2760,14 +2748,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AC-6XL</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -2782,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2807,12 +2795,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA78203</t>
+          <t>FBA78204</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2822,14 +2810,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AM-C30</t>
+          <t>AM-C31</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2844,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2869,12 +2857,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA78204</t>
+          <t>FBA78205</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0C539RBGL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2884,14 +2872,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AM-C31</t>
+          <t>AM-C32</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2906,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2931,12 +2919,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA78205</t>
+          <t>FBA78420</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0C539RBGL</t>
+          <t>B0C5957W3P</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2946,14 +2934,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AM-C32</t>
+          <t>AM-C33</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2968,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2993,12 +2981,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA78420</t>
+          <t>FBA78423</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0C5957W3P</t>
+          <t>B0C598Q6PT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3008,14 +2996,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AM-C33</t>
+          <t>AM-C36</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3030,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -3055,12 +3043,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA78423</t>
+          <t>FBA78425</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0C598Q6PT</t>
+          <t>B0C55QXL83</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3070,14 +3058,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AM-C36</t>
+          <t>AM-C38</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3092,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3117,12 +3105,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA78425</t>
+          <t>FBA78925</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B0C55QXL83</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3132,14 +3120,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AM-C38</t>
+          <t>AM-C11X</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3154,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -3179,12 +3167,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA78925</t>
+          <t>FBA78960</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3194,14 +3182,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AM-C11X</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -3216,10 +3204,10 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3241,12 +3229,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA78960</t>
+          <t>FBA78961</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0CBCB9S14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3256,14 +3244,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AM-C40</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -3278,10 +3266,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -3303,12 +3291,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA78961</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B0CBCB9S14</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3318,14 +3306,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AM-C40</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -3340,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3365,12 +3353,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3380,14 +3368,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F48" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3402,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -3427,12 +3415,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3442,11 +3430,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F49" t="n">
         <v>23</v>
@@ -3461,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3489,12 +3477,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA78976</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3504,14 +3492,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AA-22</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F50" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -3526,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -3551,12 +3539,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA78976</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3566,14 +3554,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AA-22</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F51" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3585,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -3613,12 +3601,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3628,14 +3616,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -3647,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3675,12 +3663,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA79008</t>
+          <t>FBA79009</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3690,14 +3678,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F53" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -3712,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -3737,12 +3725,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA79009</t>
+          <t>FBA79010</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,14 +3740,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3771,13 +3759,13 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -3799,12 +3787,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA79010</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3814,14 +3802,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E55" t="n">
+        <v>13</v>
+      </c>
+      <c r="F55" t="n">
         <v>9</v>
-      </c>
-      <c r="F55" t="n">
-        <v>5</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -3836,10 +3824,10 @@
         <v>4</v>
       </c>
       <c r="K55" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -3861,12 +3849,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA79014</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CH4WFQF6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3876,14 +3864,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AI-09</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -3895,13 +3883,13 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -3923,12 +3911,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FBA79014</t>
+          <t>FBA79016</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B0CH4WFQF6</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3938,14 +3926,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AI-09</t>
+          <t>AM-C3a</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -3957,10 +3945,10 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3985,12 +3973,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA79016</t>
+          <t>FBA79064</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4000,14 +3988,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AM-C3a</t>
+          <t>AA-25</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -4019,10 +4007,10 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K58" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -4047,12 +4035,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA79064</t>
+          <t>FBA79103</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4062,17 +4050,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AA-25</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -4081,10 +4069,10 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -4109,12 +4097,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA79103</t>
+          <t>FBA79104</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4124,17 +4112,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>AI-11</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -4143,10 +4131,10 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4171,12 +4159,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA79104</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4186,32 +4174,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AI-11</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E61" t="n">
+        <v>10</v>
+      </c>
+      <c r="F61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2</v>
+      </c>
+      <c r="K61" t="n">
+        <v>37</v>
+      </c>
+      <c r="L61" t="n">
         <v>27</v>
-      </c>
-      <c r="F61" t="n">
-        <v>23</v>
-      </c>
-      <c r="G61" t="n">
-        <v>4</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>27</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -4233,12 +4221,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4248,14 +4236,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F62" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -4267,13 +4255,13 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="L62" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -4295,12 +4283,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4310,14 +4298,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -4332,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -4357,12 +4345,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA79108</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4372,14 +4360,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AM-W16</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -4391,10 +4379,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -4419,12 +4407,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA79108</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4434,14 +4422,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AM-W16</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F65" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -4453,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -4481,12 +4469,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA79230</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4496,14 +4484,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -4518,7 +4506,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -4543,12 +4531,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA79230</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4558,14 +4546,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AM-W46</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4577,10 +4565,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -4605,12 +4593,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA79356</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4620,14 +4608,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AA-19WL</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -4639,10 +4627,10 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -4667,12 +4655,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA79356</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4682,14 +4670,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AA-19WL</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -4704,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -4729,12 +4717,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4744,14 +4732,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F70" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -4766,7 +4754,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -4791,12 +4779,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA79444</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4806,14 +4794,14 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F71" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -4825,13 +4813,13 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -4853,12 +4841,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA79444</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4868,14 +4856,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -4887,10 +4875,10 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="L72" t="n">
         <v>1</v>
@@ -4915,12 +4903,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79446</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4930,14 +4918,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AM-W33</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -4952,10 +4940,10 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -4977,12 +4965,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA79446</t>
+          <t>FBA79447</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4992,14 +4980,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F74" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -5011,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K74" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -5039,12 +5027,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA79447</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5054,14 +5042,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F75" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -5073,10 +5061,10 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -5101,12 +5089,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA79449</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5116,14 +5104,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AM-W36</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F76" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -5138,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -5163,12 +5151,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA79449</t>
+          <t>FBA79465</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5178,14 +5166,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AM-W36</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -5200,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -5225,12 +5213,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA79465</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5240,14 +5228,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -5262,10 +5250,10 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -5287,12 +5275,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA79653</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5302,14 +5290,14 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AM-C45 Pro</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F79" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -5321,13 +5309,13 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K79" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="L79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -5349,12 +5337,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA79653</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5364,11 +5352,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AM-C45 Pro</t>
+          <t>AM-C11 Pro</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F80" t="n">
         <v>2</v>
@@ -5383,10 +5371,10 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K80" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -5411,12 +5399,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA79655</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5426,14 +5414,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AM-C11 Pro</t>
+          <t>AM-C44 Pro</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -5445,10 +5433,10 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K81" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -5473,12 +5461,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA79655</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5488,14 +5476,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AM-C44 Pro</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -5507,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -5535,12 +5523,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5550,17 +5538,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F83" t="n">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -5575,10 +5563,10 @@
         <v>103</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -5597,12 +5585,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA79722</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5612,17 +5600,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="F84" t="n">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="G84" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -5634,13 +5622,13 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -5659,12 +5647,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA79722</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5674,14 +5662,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -5693,16 +5681,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -5721,12 +5709,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5736,14 +5724,14 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>183</v>
       </c>
       <c r="F86" t="n">
-        <v>5</v>
+        <v>182</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -5755,13 +5743,13 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>184</v>
+      </c>
+      <c r="L86" t="n">
         <v>1</v>
-      </c>
-      <c r="K86" t="n">
-        <v>7</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>1</v>
@@ -5783,12 +5771,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA79814</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0GNM35G8X</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5798,14 +5786,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AH-50 Ear Cushion</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>183</v>
+        <v>38</v>
       </c>
       <c r="F87" t="n">
-        <v>182</v>
+        <v>38</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -5820,13 +5808,13 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -5845,12 +5833,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79814</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0GNM35G8X</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5860,14 +5848,14 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AH-50 Ear Cushion</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F88" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -5882,7 +5870,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -5907,12 +5895,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5922,14 +5910,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F89" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -5944,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -5969,12 +5957,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79820</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5984,14 +5972,14 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -6006,7 +5994,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -6031,12 +6019,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA79821</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6046,14 +6034,14 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="F91" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -6065,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K91" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -6093,12 +6081,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79821</t>
+          <t>FBA79822</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6108,14 +6096,14 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+          <t>KB-01 (AM-W32 + AI-12)</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -6127,10 +6115,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -6155,12 +6143,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA79822</t>
+          <t>FBA79823</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6170,7 +6158,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>KB-01 (AM-W32 + AI-12)</t>
+          <t>PB-01 (AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -6217,12 +6205,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA79823</t>
+          <t>FBA79824</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6232,14 +6220,14 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PB-01 (AM-C11 + AI-04)</t>
+          <t>GB-01 (AM-C43 +AI-10)</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -6251,10 +6239,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -6279,12 +6267,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79824</t>
+          <t>FBA79825</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6294,14 +6282,14 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>GB-01 (AM-C43 +AI-10)</t>
+          <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -6313,10 +6301,10 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
         <v>4</v>
-      </c>
-      <c r="K95" t="n">
-        <v>6</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -6341,12 +6329,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79825</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6356,14 +6344,14 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F96" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -6378,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -6403,12 +6391,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA79826</t>
+          <t>FBA79827</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6418,14 +6406,14 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F97" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -6437,10 +6425,10 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -6465,12 +6453,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79827</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6480,17 +6468,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F98" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -6499,10 +6487,10 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -6527,12 +6515,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA79831</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6542,17 +6530,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>GB-04 (AM-C45 + AI-06)</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F99" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -6561,10 +6549,10 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K99" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -6589,12 +6577,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79831</t>
+          <t>FBA79832</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6604,14 +6592,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>GB-04 (AM-C45 + AI-06)</t>
+          <t>GB-05 (AM-C43 + AI-06)</t>
         </is>
       </c>
       <c r="E100" t="n">
         <v>5</v>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -6623,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K100" t="n">
         <v>5</v>
@@ -6651,12 +6639,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA79832</t>
+          <t>FBA79833</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6666,11 +6654,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>GB-05 (AM-C43 + AI-06)</t>
+          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F101" t="n">
         <v>4</v>
@@ -6685,10 +6673,10 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K101" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -6713,12 +6701,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA79833</t>
+          <t>FBA79834</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0FJ8T4WXM</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6728,14 +6716,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
+          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -6747,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -6775,12 +6763,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79834</t>
+          <t>FBA79835</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0FJ8T4WXM</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6790,29 +6778,29 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
+          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
         </is>
       </c>
       <c r="E103" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
         <v>2</v>
       </c>
-      <c r="F103" t="n">
-        <v>2</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
       <c r="K103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -6837,12 +6825,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79835</t>
+          <t>FBA79836</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0FJ8Z1W81</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6852,14 +6840,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6871,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -6899,12 +6887,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA79836</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0FJ8Z1W81</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6914,14 +6902,14 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="F105" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -6936,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -6961,12 +6949,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6976,14 +6964,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="F106" t="n">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -6998,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -7023,12 +7011,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7038,14 +7026,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AH-60-RD</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F107" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -7057,10 +7045,10 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K107" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -7085,12 +7073,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7100,14 +7088,14 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>AH-60-RD</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F108" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -7119,10 +7107,10 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K108" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -7147,12 +7135,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7162,14 +7150,14 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>AH-60-BL</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F109" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -7181,10 +7169,10 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -7209,12 +7197,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA79845</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7224,14 +7212,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F110" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -7246,7 +7234,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
@@ -7271,12 +7259,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA79845</t>
+          <t>FBA79846</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7286,14 +7274,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>AM-C11X Pro</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F111" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -7305,13 +7293,13 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K111" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -7333,12 +7321,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA79846</t>
+          <t>FBA79847</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7348,11 +7336,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>AM-C11X Pro</t>
+          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -7367,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K112" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -7395,12 +7383,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA79847</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7410,14 +7398,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -7429,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K113" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -7457,12 +7445,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79903</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0FR5DLXH9</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7472,14 +7460,14 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AA-25M</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F114" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -7491,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -7519,12 +7507,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA79903</t>
+          <t>FBA79904</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0FR5DLXH9</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7534,14 +7522,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>AA-25M</t>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F115" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -7556,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -7581,12 +7569,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA79904</t>
+          <t>FBA79905</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7596,14 +7584,14 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F116" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -7618,7 +7606,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -7643,12 +7631,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79905</t>
+          <t>FBA79906</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7658,14 +7646,14 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F117" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -7680,7 +7668,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -7705,12 +7693,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79906</t>
+          <t>FBA79907</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0FTVS34SD</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7720,14 +7708,14 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+          <t>PB-13 (AM-C43+AH-40-SL+AI-11)</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -7742,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -7767,12 +7755,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA79907</t>
+          <t>FBA79908</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0FTVS34SD</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7782,17 +7770,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PB-13 (AM-C43+AH-40-SL+AI-11)</t>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -7804,10 +7792,10 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
@@ -7829,12 +7817,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA79908</t>
+          <t>FBA79909</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7844,17 +7832,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -7866,7 +7854,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="L120" t="n">
         <v>1</v>
@@ -7891,12 +7879,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA79909</t>
+          <t>FBA79956</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0FVM17Q4W</t>
+          <t>B0GMPGNXX3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7906,14 +7894,14 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>A3-XLR</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="F121" t="n">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -7925,13 +7913,13 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -7953,12 +7941,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79956</t>
+          <t>FBA79957</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0GMPGNXX3</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7968,14 +7956,14 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>A3-XLR</t>
+          <t>AM-W23</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="F122" t="n">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -7987,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="K122" t="n">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -8015,12 +8003,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79957</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8030,14 +8018,14 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F123" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -8049,16 +8037,16 @@
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K123" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -8077,12 +8065,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8092,14 +8080,14 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>AM-W47 Wired</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F124" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -8111,16 +8099,16 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
@@ -8139,12 +8127,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8154,14 +8142,14 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>AM-W47 Wired</t>
+          <t>AM-W47 Wireless</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="F125" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -8173,10 +8161,10 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -8201,12 +8189,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8216,14 +8204,14 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>AM-W47 Wireless</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="F126" t="n">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -8235,16 +8223,16 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -8263,12 +8251,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA79962</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8278,14 +8266,14 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>BE-4T</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="F127" t="n">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -8297,16 +8285,16 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -8325,12 +8313,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA79962</t>
+          <t>FBA79963</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8340,14 +8328,14 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>BE-4T</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -8362,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -8387,12 +8375,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA79963</t>
+          <t>FBA79964</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8402,14 +8390,14 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>AM-Pro8</t>
+          <t>AM-Pro12</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -8424,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -8449,12 +8437,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA79964</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8464,14 +8452,14 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>AM-Pro12</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -8486,7 +8474,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -8511,12 +8499,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8526,14 +8514,14 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -8548,10 +8536,10 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
@@ -8573,12 +8561,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79967</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8588,14 +8576,14 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>113</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -8607,13 +8595,13 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132" t="n">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="L132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -8635,12 +8623,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA79967</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8650,14 +8638,14 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>114</v>
+        <v>7</v>
       </c>
       <c r="F133" t="n">
-        <v>114</v>
+        <v>7</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -8672,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>114</v>
+        <v>7</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -8697,12 +8685,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79969</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8712,14 +8700,14 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>UB-03 (AM-S1 + AA-22)</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F134" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -8731,10 +8719,10 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K134" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -8759,12 +8747,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA79969</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8774,14 +8762,14 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>UB-03 (AM-S1 + AA-22)</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F135" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -8793,10 +8781,10 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -8821,12 +8809,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79974</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0GD8JSPB1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8836,14 +8824,14 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F136" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -8858,7 +8846,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -8883,12 +8871,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79974</t>
+          <t>FBA79975</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0GD8JSPB1</t>
+          <t>B0GXP7LJ75</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8898,14 +8886,14 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AE831</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F137" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -8920,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -8945,12 +8933,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79975</t>
+          <t>FBA79979</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0GXP7LJ75</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8960,14 +8948,14 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AE831</t>
+          <t>AK-37-B</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F138" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -8982,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -9007,12 +8995,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79979</t>
+          <t>FBA79980</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9022,14 +9010,14 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>AK-37-W</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F139" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -9041,10 +9029,10 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K139" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -9069,12 +9057,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA79980</t>
+          <t>FBA79981</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9084,14 +9072,14 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>AK-61 Neo</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F140" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -9103,10 +9091,10 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -9131,12 +9119,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA79981</t>
+          <t>FBA79982</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9146,14 +9134,14 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>AK-61 Neo</t>
+          <t>AK-61 Pro</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F141" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -9168,7 +9156,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -9193,12 +9181,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA79982</t>
+          <t>FBA79995</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9208,14 +9196,14 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>AK-61 Pro</t>
+          <t>AM-C50</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="F142" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -9230,7 +9218,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -9255,12 +9243,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FBA79995</t>
+          <t>FBA79996</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9270,14 +9258,14 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>AM-C49</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F143" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -9292,7 +9280,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -9317,12 +9305,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FBA79996</t>
+          <t>FBA79997</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0GW9461N5</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9332,14 +9320,14 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -9354,7 +9342,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -9379,12 +9367,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FBA79997</t>
+          <t>FBA79998</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B0GW9461N5</t>
+          <t>B0GW8YC59C</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9394,14 +9382,14 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -9416,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -9441,12 +9429,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FBA79998</t>
+          <t>FBA79999</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B0GW8YC59C</t>
+          <t>B0GW92TVVC</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9456,14 +9444,14 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>JTG800</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -9478,7 +9466,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -9503,12 +9491,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FBA79999</t>
+          <t>FBA80000</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>B0GW92TVVC</t>
+          <t>B0GW8XGPB2</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9518,14 +9506,14 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>JTG800</t>
+          <t>DP-718H</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -9540,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -9565,12 +9553,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FBA80000</t>
+          <t>FBA80001</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B0GW8XGPB2</t>
+          <t>B0GW92TQGV</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9580,14 +9568,14 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>DP-718H</t>
+          <t>USB718</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F148" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -9599,10 +9587,10 @@
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -9627,12 +9615,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FBA80001</t>
+          <t>FBA80002</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>B0GW92TQGV</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9642,14 +9630,14 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>USB718</t>
+          <t>AM-W33 Pro</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -9661,10 +9649,10 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -9689,12 +9677,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FBA80002</t>
+          <t>FBA80003</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9704,7 +9692,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>AM-W33 Pro</t>
+          <t>AM-W32 Pro</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -9751,12 +9739,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FBA80003</t>
+          <t>FBA80004</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9766,14 +9754,14 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>AM-W32 Pro</t>
+          <t>AM-W36 Pro</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F151" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -9788,7 +9776,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -9813,12 +9801,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FBA80004</t>
+          <t>FBA80005</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0GW96CQMG</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9828,14 +9816,14 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>AM-W36 Pro</t>
+          <t>T-835</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -9850,7 +9838,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -9875,12 +9863,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FBA80005</t>
+          <t>FBA80007</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>B0GW96CQMG</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9890,14 +9878,14 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>T-835</t>
+          <t>MT-12</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -9912,7 +9900,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -9937,12 +9925,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FBA80007</t>
+          <t>FBA80009</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9952,14 +9940,14 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="F154" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -9974,7 +9962,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -9999,12 +9987,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FBA80009</t>
+          <t>FBA80010</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10014,14 +10002,14 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>AM-C52</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F155" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -10036,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -10061,12 +10049,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FBA80010</t>
+          <t>FBA80011</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0GTZND3ZN</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10076,14 +10064,14 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>AM-C52</t>
+          <t>AM-Pro16</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -10098,10 +10086,10 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M156" t="n">
         <v>0</v>
@@ -10123,12 +10111,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FBA80011</t>
+          <t>FBA80012</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>B0GTZND3ZN</t>
+          <t>B0GTZJF142</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10138,7 +10126,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>AM-Pro16</t>
+          <t>AM-Pro24</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -10185,12 +10173,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FBA80012</t>
+          <t>FBA80016</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>B0GTZJF142</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10200,14 +10188,14 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>AM-Pro24</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -10222,10 +10210,10 @@
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
@@ -10247,12 +10235,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FBA80016</t>
+          <t>FBA80074</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0GY827J9C</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10262,14 +10250,14 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F159" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -10284,10 +10272,10 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -10309,12 +10297,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FBA80074</t>
+          <t>FBA80075</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>B0GY827J9C</t>
+          <t>B0GXPGBQB1</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10324,14 +10312,14 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
+          <t>PB-16 (AH-50+AI-13+AM-C2)</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F160" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -10346,10 +10334,10 @@
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -10371,12 +10359,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FBA80075</t>
+          <t>FBA80076</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>B0GXPGBQB1</t>
+          <t>B0GY857139</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10386,14 +10374,14 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>PB-16 (AH-50+AI-13+AM-C2)</t>
+          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -10408,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -10433,12 +10421,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FBA80076</t>
+          <t>FBA80077</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>B0GY857139</t>
+          <t>B0GY86ZT1X</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10448,14 +10436,14 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
+          <t>PB-18 (AH-45-BK+AI-03+AM-C39)</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -10470,7 +10458,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -10495,12 +10483,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FBA80077</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>B0GY86ZT1X</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10510,14 +10498,14 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>PB-18 (AH-45-BK+AI-03+AM-C39)</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F163" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -10529,10 +10517,10 @@
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -10557,12 +10545,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10572,14 +10560,14 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F164" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -10594,7 +10582,7 @@
         <v>1</v>
       </c>
       <c r="K164" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -10619,12 +10607,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA80104</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0GXY7YJWP</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10634,14 +10622,14 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -10656,7 +10644,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -10681,12 +10669,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FBA80104</t>
+          <t>FBA80105</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>B0GXY7YJWP</t>
+          <t>B0H2FNV2RC</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10696,7 +10684,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
+          <t>UB-05 (AM-S2+AA-21)</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -10743,12 +10731,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FBA80105</t>
+          <t>FBA80106</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>B0H2FNV2RC</t>
+          <t>B0H2FCK54H</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10758,11 +10746,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>UB-05 (AM-S2+AA-21)</t>
+          <t>UB-06 (AM-S2+AA-22)</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -10780,13 +10768,13 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
@@ -10805,12 +10793,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FBA80106</t>
+          <t>FBA80109</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>B0H2FCK54H</t>
+          <t>B0H2ZCQFTZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10820,17 +10808,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>UB-06 (AM-S2+AA-22)</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -10842,13 +10830,13 @@
         <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -10867,12 +10855,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FBA80109</t>
+          <t>FBA80110</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>B0H2ZCQFTZ</t>
+          <t>B0H2Z6R6V8</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10882,14 +10870,14 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>X5</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
         <v>5</v>
@@ -10904,7 +10892,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -10929,12 +10917,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FBA80110</t>
+          <t>FBA80128</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>B0H2Z6R6V8</t>
+          <t>B0H1H3K6B2</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10944,17 +10932,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>X5</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G170" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -10966,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -10991,12 +10979,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FBA80128</t>
+          <t>FBA80141</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>B0H1H3K6B2</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -11006,14 +10994,14 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -11028,7 +11016,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -11053,12 +11041,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FBA80141</t>
+          <t>FBA80142</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>B0FJS57732</t>
+          <t>B0H3LHF2WW</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11068,14 +11056,14 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-C5 White</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -11087,10 +11075,10 @@
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -11115,12 +11103,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FBA80142</t>
+          <t>FBA80143</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>B0H3LHF2WW</t>
+          <t>B0H1MTP2ZP</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11130,14 +11118,14 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>AM-C5 White</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F173" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -11152,7 +11140,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -11177,12 +11165,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FBA80143</t>
+          <t>FBI76864</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>B0H1MTP2ZP</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11192,14 +11180,14 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -11214,7 +11202,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -11239,12 +11227,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FBI76864</t>
+          <t>FBK79009</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11254,14 +11242,14 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -11276,7 +11264,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -11301,12 +11289,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FBK79009</t>
+          <t>FBK79010</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11316,14 +11304,14 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F176" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -11338,10 +11326,10 @@
         <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M176" t="n">
         <v>0</v>
@@ -11363,12 +11351,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FBK79010</t>
+          <t>FBK79708</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0FJS7JZ4V</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11378,14 +11366,14 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F177" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -11400,13 +11388,13 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L177" t="n">
+        <v>2</v>
+      </c>
+      <c r="M177" t="n">
         <v>1</v>
-      </c>
-      <c r="M177" t="n">
-        <v>0</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
@@ -11425,12 +11413,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FBK79708</t>
+          <t>FBM79783</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>B0FJS7JZ4V</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11440,14 +11428,14 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -11462,13 +11450,13 @@
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="L178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
@@ -11487,12 +11475,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FBM79783</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>B0FJS57732</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11502,14 +11490,14 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -11524,17 +11512,17 @@
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M179" t="n">
         <v>0</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>AUDIOARRAY</t>
+          <t>CAMBIUMRETAIL</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -11549,12 +11537,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11564,7 +11552,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -11586,10 +11574,10 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
         <v>0</v>
@@ -11611,12 +11599,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11626,7 +11614,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -11673,12 +11661,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA75676</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11688,7 +11676,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-C4</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -11720,7 +11708,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>CAMBIUMRETAIL</t>
+          <t>VIOMI</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -11735,12 +11723,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FBA75676</t>
+          <t>FBA75677</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11750,14 +11738,14 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>AM-C4</t>
+          <t>AM-C5</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -11772,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -11797,12 +11785,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FBA75677</t>
+          <t>FBA75683</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11812,14 +11800,14 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>AM-C5</t>
+          <t>AA-03</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -11834,7 +11822,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -11859,12 +11847,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FBA75683</t>
+          <t>FBA75690</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11874,14 +11862,14 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>AA-03</t>
+          <t>AM-C10</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -11896,7 +11884,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -11921,12 +11909,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FBA75690</t>
+          <t>FBA78423</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0C598Q6PT</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11936,7 +11924,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>AM-C10</t>
+          <t>AM-C36</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -11983,12 +11971,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FBA78423</t>
+          <t>FBA78960</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>B0C598Q6PT</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11998,7 +11986,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>AM-C36</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -12045,12 +12033,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FBA78960</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12060,14 +12048,14 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -12082,7 +12070,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -12107,12 +12095,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12122,14 +12110,14 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -12144,7 +12132,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -12169,12 +12157,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12184,14 +12172,14 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -12206,7 +12194,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -12231,12 +12219,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA79444</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12246,7 +12234,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -12293,12 +12281,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FBA79444</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12308,14 +12296,14 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -12330,7 +12318,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -12355,12 +12343,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12370,14 +12358,14 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F193" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -12392,7 +12380,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -12417,12 +12405,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA79722</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12432,7 +12420,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -12479,12 +12467,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FBA79722</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12494,7 +12482,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -12541,12 +12529,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12556,14 +12544,14 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -12578,7 +12566,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -12588,7 +12576,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>VIOMI</t>
+          <t>WHITEMULBERRY</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -12597,68 +12585,6 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>FBA76864</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>B0BPLZ5CGV</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>AI-04 Red</t>
-        </is>
-      </c>
-      <c r="E197" t="n">
-        <v>0</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" t="n">
-        <v>0</v>
-      </c>
-      <c r="H197" t="n">
-        <v>0</v>
-      </c>
-      <c r="I197" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" t="n">
-        <v>0</v>
-      </c>
-      <c r="L197" t="n">
-        <v>0</v>
-      </c>
-      <c r="M197" t="n">
-        <v>0</v>
-      </c>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>WHITEMULBERRY</t>
-        </is>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="P197" t="n">
         <v>29</v>
       </c>
     </row>

--- a/data/raw/inventory/Week 29/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -538,10 +538,10 @@
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -2321,7 +2321,7 @@
         <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>13</v>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F37" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2708,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4196,10 +4196,10 @@
         <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L61" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>27</v>
       </c>
       <c r="F90" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -5991,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
         <v>27</v>
@@ -7154,10 +7154,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F113" t="n">
         <v>35</v>
@@ -7417,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K113" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F133" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -8660,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 29/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F2" t="n">
         <v>129</v>
@@ -535,10 +535,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L20" t="n">
         <v>2</v>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2457,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2522,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="K34" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
         <v>63</v>
       </c>
       <c r="F37" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>63</v>
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F49" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3455,7 +3455,7 @@
         <v>24</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F51" t="n">
         <v>28</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
         <v>4</v>
       </c>
       <c r="K55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L55" t="n">
         <v>1</v>
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F61" t="n">
         <v>8</v>
@@ -4193,10 +4193,10 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L61" t="n">
         <v>28</v>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F76" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -5250,10 +5250,10 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F83" t="n">
         <v>81</v>
@@ -5557,10 +5557,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
         <v>26</v>
@@ -5991,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F98" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G98" t="n">
         <v>3</v>
@@ -6490,7 +6490,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F106" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F108" t="n">
         <v>4</v>
@@ -7107,10 +7107,10 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K108" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -7154,10 +7154,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F109" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F113" t="n">
         <v>35</v>
@@ -7417,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K113" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F114" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F124" t="n">
         <v>43</v>
@@ -8099,10 +8099,10 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F125" t="n">
         <v>10</v>
@@ -8161,10 +8161,10 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F126" t="n">
         <v>91</v>
@@ -8223,10 +8223,10 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F127" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -8518,10 +8518,10 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L131" t="n">
         <v>2</v>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F132" t="n">
         <v>113</v>
@@ -8595,10 +8595,10 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
         <v>17</v>
       </c>
       <c r="F133" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -8657,7 +8657,7 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133" t="n">
         <v>17</v>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F135" t="n">
         <v>8</v>
@@ -8781,10 +8781,10 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K135" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -9017,7 +9017,7 @@
         <v>23</v>
       </c>
       <c r="F139" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
         <v>23</v>
@@ -9141,7 +9141,7 @@
         <v>5</v>
       </c>
       <c r="F141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K141" t="n">
         <v>5</v>
@@ -9823,7 +9823,7 @@
         <v>5</v>
       </c>
       <c r="F152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -9835,7 +9835,7 @@
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K152" t="n">
         <v>5</v>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F159" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -10269,10 +10269,10 @@
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K159" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L159" t="n">
         <v>1</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F163" t="n">
         <v>17</v>
@@ -10517,10 +10517,10 @@
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K163" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F164" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -10582,7 +10582,7 @@
         <v>1</v>
       </c>
       <c r="K164" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -11060,10 +11060,10 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F172" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -11078,7 +11078,7 @@
         <v>1</v>
       </c>
       <c r="K172" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -11388,10 +11388,10 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
         <v>1</v>
